--- a/Tabel_Jumlah_Anomali_Ringkas.xlsx
+++ b/Tabel_Jumlah_Anomali_Ringkas.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Dashboard Monitoring Anomali\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76217F22-37BB-4921-BE25-38908045FA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DAAD5D-F2F1-4AAF-92AE-AA1E7FBFAFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Ringkas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -65,7 +78,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +98,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -123,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +166,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -458,13 +482,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -491,14 +515,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>18170</v>
-      </c>
-      <c r="D4" s="2">
-        <v>18156</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.99922949917446335</v>
-      </c>
+        <v>25328</v>
+      </c>
+      <c r="D4" s="9">
+        <f>C4-E4</f>
+        <v>25328</v>
+      </c>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
@@ -508,14 +531,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>20922</v>
-      </c>
-      <c r="D5" s="4">
-        <v>20830</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0.99560271484561702</v>
-      </c>
+        <v>45235</v>
+      </c>
+      <c r="D5" s="8">
+        <f t="shared" ref="D5" si="0">C5-E5</f>
+        <v>45235</v>
+      </c>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
@@ -525,14 +547,13 @@
         <v>7</v>
       </c>
       <c r="C6" s="2">
-        <v>14247</v>
-      </c>
-      <c r="D6" s="2">
-        <v>14239</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.99943847827612831</v>
-      </c>
+        <v>28429</v>
+      </c>
+      <c r="D6" s="8">
+        <f>C6-E6</f>
+        <v>28429</v>
+      </c>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
@@ -542,14 +563,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="4">
-        <v>7860</v>
-      </c>
-      <c r="D7" s="4">
-        <v>7742</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0.98498727735368952</v>
-      </c>
+        <v>17630</v>
+      </c>
+      <c r="D7" s="8">
+        <f t="shared" ref="D7:D9" si="1">C7-E7</f>
+        <v>17630</v>
+      </c>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -559,14 +579,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="2">
-        <v>8918</v>
-      </c>
-      <c r="D8" s="2">
-        <v>8918</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
+        <v>19210</v>
+      </c>
+      <c r="D8" s="8">
+        <f t="shared" si="1"/>
+        <v>19210</v>
+      </c>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
@@ -576,14 +595,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="4">
-        <v>6488</v>
-      </c>
-      <c r="D9" s="4">
-        <v>6432</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0.99136868064118377</v>
-      </c>
+        <v>13136</v>
+      </c>
+      <c r="D9" s="8">
+        <f t="shared" si="1"/>
+        <v>13136</v>
+      </c>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -591,14 +609,13 @@
         <v>11</v>
       </c>
       <c r="C10" s="1">
-        <v>76605</v>
-      </c>
-      <c r="D10" s="1">
-        <v>76317</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.99624045427844132</v>
-      </c>
+        <v>148968</v>
+      </c>
+      <c r="D10" s="8">
+        <f>C10-E10</f>
+        <v>148968</v>
+      </c>
+      <c r="E10" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
